--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -813,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328521</v>
+        <v>124328552</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,39 +825,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R3" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +906,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,12 +915,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328552</v>
+        <v>124328521</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,30 +966,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R4" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,7 +1056,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,28 +1065,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328518</v>
+        <v>124328552</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R2" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,7 +768,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +777,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -813,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +832,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,13 +872,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R3" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,7 +922,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,28 +931,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R2" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +781,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,28 +790,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328518</v>
+        <v>124328521</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,25 +825,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,14 +852,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -922,7 +915,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328521</v>
+        <v>124328552</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,39 +959,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R4" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1049,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328518</v>
+        <v>124328521</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,14 +714,10 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -781,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328521</v>
+        <v>124328552</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,39 +821,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R3" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +902,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,12 +911,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +966,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R4" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,7 +1056,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,28 +1065,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,26 +825,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R3" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +915,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,28 +924,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328518</v>
+        <v>124328552</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,39 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R4" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1049,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328518</v>
+        <v>124328552</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,39 +825,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R3" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +902,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,12 +911,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,26 +966,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R4" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,7 +1056,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,28 +1065,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328521</v>
+        <v>124328518</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -777,7 +781,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328552</v>
+        <v>124328521</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,30 +825,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R3" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +915,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,28 +924,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328518</v>
+        <v>124328552</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,39 +963,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R4" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1049,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328518</v>
+        <v>124328521</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,14 +714,10 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -781,7 +777,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328552</v>
+        <v>124328518</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,26 +825,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,13 +865,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R3" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,7 +915,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,28 +924,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328521</v>
+        <v>124328552</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>74713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,39 +959,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,13 +990,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R4" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1049,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124328521</v>
+        <v>124328518</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,14 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -777,7 +781,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,10 +813,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328518</v>
+        <v>124328552</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,39 +829,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +856,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518834</v>
+        <v>518830</v>
       </c>
       <c r="R3" t="n">
-        <v>6339129</v>
+        <v>6339104</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,7 +906,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>På flera träd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,12 +915,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -947,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328552</v>
+        <v>124328521</v>
       </c>
       <c r="B4" t="n">
-        <v>74713</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,30 +966,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -990,13 +1006,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518830</v>
+        <v>518834</v>
       </c>
       <c r="R4" t="n">
-        <v>6339104</v>
+        <v>6339129</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,7 +1056,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera träd.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,28 +1065,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 51425-2024 artfynd.xlsx
+++ b/artfynd/A 51425-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124328552</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,15 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124328518</v>
+        <v>124328521</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -855,14 +845,10 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -922,7 +908,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stött ur tall.</t>
+          <t>Födosökande på granhögstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,37 +940,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124328521</v>
+        <v>124328518</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,10 +974,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1056,7 +1041,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande på granhögstubbe.</t>
+          <t>Stött ur tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
